--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6228070175438597</v>
+        <v>0.6583333333333333</v>
       </c>
       <c r="B2">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.6382978723404256</v>
+        <v>0.647887323943662</v>
       </c>
       <c r="D2">
-        <v>0.4146341463414634</v>
+        <v>0.3875968992248062</v>
       </c>
       <c r="E2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>9</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.6583333333333333</v>
+        <v>0.6910569105691057</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.647887323943662</v>
+        <v>0.6830985915492958</v>
       </c>
       <c r="D2">
-        <v>0.3875968992248062</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
